--- a/Result/profitability/6264.xlsx
+++ b/Result/profitability/6264.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.75</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.19375</v>
+        <v>-0.19625</v>
       </c>
       <c r="N2" t="n">
-        <v>11.40875</v>
+        <v>20.435</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.24</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.19125</v>
+        <v>-0.24875</v>
       </c>
       <c r="N3" t="n">
-        <v>16.5175</v>
+        <v>21.04125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2225</v>
+        <v>-0.2325</v>
       </c>
       <c r="N4" t="n">
-        <v>14.91</v>
+        <v>20.4925</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.23625</v>
+        <v>-0.24625</v>
       </c>
       <c r="N5" t="n">
-        <v>12.71625</v>
+        <v>20.04875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1140,7 +1140,7 @@
         <v>-0.215</v>
       </c>
       <c r="N6" t="n">
-        <v>15.07875</v>
+        <v>18.61875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.24125</v>
+        <v>-0.29875</v>
       </c>
       <c r="N7" t="n">
-        <v>14.78375</v>
+        <v>20.0275</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>-0.38</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.31125</v>
+        <v>-0.31875</v>
       </c>
       <c r="N8" t="n">
-        <v>14.4325</v>
+        <v>23.49125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>-0.22</v>
       </c>
       <c r="N13" t="n">
-        <v>7.18</v>
+        <v>7.180000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9800,6 +9800,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6264</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>35</v>
+      </c>
+      <c r="D75" t="n">
+        <v>14</v>
+      </c>
+      <c r="E75" t="n">
+        <v>21</v>
+      </c>
+      <c r="F75" t="n">
+        <v>59.78</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-29</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-81.56%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-19</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-48</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-38</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.135</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.4725</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.06000000000000003</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2727272727272729</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>72.47</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-5.710795902285264</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.08000000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>58.66</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>52.37499999999999</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
